--- a/EUt.xlsx
+++ b/EUt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Medina_Admin\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36E1D2E-5B28-4CC6-B3F5-45E2607DB277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB89A8EE-985B-4616-AE27-D30A93853642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2640" yWindow="2640" windowWidth="18514" windowHeight="11511" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -305,9 +305,6 @@
     <t>Material Science</t>
   </si>
   <si>
-    <t>Multimedia</t>
-  </si>
-  <si>
     <t>h_da Einrichtung</t>
   </si>
   <si>
@@ -324,6 +321,9 @@
   </si>
   <si>
     <t>Accelerate  Beteiligung</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
 </sst>
 </file>
@@ -720,10 +720,10 @@
   <sheetData>
     <row r="1" spans="1:12" ht="36" customHeight="1" thickBot="1">
       <c r="A1" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>3</v>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -2345,7 +2345,7 @@
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
@@ -2395,7 +2395,7 @@
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -2445,7 +2445,7 @@
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
@@ -2471,7 +2471,7 @@
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
@@ -2589,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="L93" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="16.5" customHeight="1">
@@ -2640,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="L96" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -2770,7 +2770,7 @@
         <v>72</v>
       </c>
       <c r="F104" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>75</v>

--- a/EUt.xlsx
+++ b/EUt.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Medina_Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Medina_Admin\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF61F5B4-776C-4AC1-95D7-9F4598FBC37D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A10FCC-7C47-4272-A9A1-39049E7E3BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25395" yWindow="2445" windowWidth="21855" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -482,10 +482,6 @@
     <t>Matthias Maier</t>
   </si>
   <si>
-    <t>Accelerate 
-Beteiligung</t>
-  </si>
-  <si>
     <t>ja</t>
   </si>
   <si>
@@ -634,6 +630,9 @@
   </si>
   <si>
     <t>Media</t>
+  </si>
+  <si>
+    <t>Accelerate Beteiligung</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>146</v>
+        <v>196</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>32</v>
@@ -1047,16 +1046,16 @@
         <v>98</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -1064,10 +1063,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K2" t="s">
         <v>3</v>
@@ -1081,7 +1080,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
         <v>82</v>
@@ -1090,7 +1089,7 @@
         <v>83</v>
       </c>
       <c r="J3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K3" t="s">
         <v>5</v>
@@ -1104,10 +1103,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K4" t="s">
         <v>3</v>
@@ -1121,13 +1120,13 @@
         <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
         <v>87</v>
       </c>
       <c r="J5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K5" t="s">
         <v>5</v>
@@ -1141,10 +1140,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K6" t="s">
         <v>3</v>
@@ -1158,7 +1157,7 @@
         <v>68</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>70</v>
@@ -1170,7 +1169,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>3</v>
@@ -1184,7 +1183,7 @@
         <v>69</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>70</v>
@@ -1196,7 +1195,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -1210,10 +1209,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K9" t="s">
         <v>5</v>
@@ -1227,13 +1226,13 @@
         <v>11</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C10" t="s">
         <v>71</v>
       </c>
       <c r="J10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K10" t="s">
         <v>3</v>
@@ -1247,13 +1246,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
         <v>133</v>
       </c>
       <c r="J11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K11" t="s">
         <v>3</v>
@@ -1267,10 +1266,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K12" t="s">
         <v>3</v>
@@ -1284,16 +1283,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K13" t="s">
         <v>3</v>
       </c>
       <c r="L13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1301,10 +1300,10 @@
         <v>16</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K14" t="s">
         <v>5</v>
@@ -1318,13 +1317,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C15" t="s">
         <v>73</v>
       </c>
       <c r="J15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K15" t="s">
         <v>3</v>
@@ -1338,7 +1337,7 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D16" t="s">
         <v>81</v>
@@ -1347,7 +1346,7 @@
         <v>95</v>
       </c>
       <c r="J16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K16" t="s">
         <v>5</v>
@@ -1361,10 +1360,10 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K17" t="s">
         <v>3</v>
@@ -1378,10 +1377,10 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -1395,10 +1394,10 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -1412,10 +1411,10 @@
         <v>135</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
@@ -1429,13 +1428,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D21" t="s">
         <v>84</v>
       </c>
       <c r="J21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K21" t="s">
         <v>3</v>
@@ -1449,13 +1448,13 @@
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D22" t="s">
         <v>85</v>
       </c>
       <c r="J22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K22" t="s">
         <v>3</v>
@@ -1469,13 +1468,13 @@
         <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C23" t="s">
         <v>67</v>
       </c>
       <c r="J23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K23" t="s">
         <v>3</v>
@@ -1489,10 +1488,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K24" t="s">
         <v>5</v>
@@ -1506,7 +1505,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4" t="s">
@@ -1518,13 +1517,13 @@
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>5</v>
       </c>
       <c r="L25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -1532,13 +1531,13 @@
         <v>27</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C26" t="s">
         <v>72</v>
       </c>
       <c r="J26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K26" t="s">
         <v>3</v>
@@ -1552,19 +1551,19 @@
         <v>28</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>86</v>
       </c>
       <c r="J27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K27" t="s">
         <v>3</v>
       </c>
       <c r="L27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1572,13 +1571,13 @@
         <v>29</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E28" t="s">
         <v>96</v>
       </c>
       <c r="J28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K28" t="s">
         <v>5</v>
@@ -1592,13 +1591,13 @@
         <v>30</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C29" t="s">
         <v>79</v>
       </c>
       <c r="J29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K29" t="s">
         <v>3</v>
@@ -1612,13 +1611,13 @@
         <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C30" t="s">
         <v>77</v>
       </c>
       <c r="J30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K30" t="s">
         <v>5</v>
@@ -1632,13 +1631,13 @@
         <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C31" t="s">
         <v>77</v>
       </c>
       <c r="J31" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K31" t="s">
         <v>3</v>
@@ -1652,7 +1651,7 @@
         <v>76</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>78</v>
@@ -1664,7 +1663,7 @@
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>3</v>
@@ -1678,13 +1677,13 @@
         <v>33</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G33" t="s">
         <v>34</v>
       </c>
       <c r="J33" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K33" t="s">
         <v>5</v>
@@ -1698,13 +1697,13 @@
         <v>35</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G34" t="s">
         <v>34</v>
       </c>
       <c r="J34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K34" t="s">
         <v>5</v>
@@ -1718,13 +1717,13 @@
         <v>10</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G35" t="s">
         <v>34</v>
       </c>
       <c r="J35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K35" t="s">
         <v>3</v>
@@ -1738,10 +1737,10 @@
         <v>103</v>
       </c>
       <c r="B36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K36" t="s">
         <v>3</v>
@@ -1755,19 +1754,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s">
         <v>66</v>
       </c>
       <c r="J37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K37" t="s">
         <v>5</v>
       </c>
       <c r="L37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -1775,13 +1774,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C38" t="s">
         <v>38</v>
       </c>
       <c r="J38" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K38" t="s">
         <v>3</v>
@@ -1795,13 +1794,13 @@
         <v>144</v>
       </c>
       <c r="B39" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F39" t="s">
         <v>40</v>
       </c>
       <c r="J39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K39" t="s">
         <v>5</v>
@@ -1815,13 +1814,13 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F40" t="s">
         <v>55</v>
       </c>
       <c r="J40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K40" t="s">
         <v>3</v>
@@ -1835,13 +1834,13 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F41" t="s">
         <v>55</v>
       </c>
       <c r="J41" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K41" t="s">
         <v>5</v>
@@ -1855,13 +1854,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I42" t="s">
         <v>44</v>
       </c>
       <c r="J42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K42" t="s">
         <v>3</v>
@@ -1875,13 +1874,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I43" t="s">
         <v>44</v>
       </c>
       <c r="J43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K43" t="s">
         <v>5</v>
@@ -1895,13 +1894,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K44" t="s">
         <v>3</v>
@@ -1915,10 +1914,10 @@
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K45" t="s">
         <v>5</v>
@@ -1932,13 +1931,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F46" t="s">
         <v>50</v>
       </c>
       <c r="J46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K46" t="s">
         <v>5</v>
@@ -1952,13 +1951,13 @@
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G47" t="s">
         <v>53</v>
       </c>
       <c r="J47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K47" t="s">
         <v>5</v>
@@ -1972,13 +1971,13 @@
         <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G48" t="s">
         <v>53</v>
       </c>
       <c r="J48" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K48" t="s">
         <v>3</v>
@@ -1992,13 +1991,13 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F49" t="s">
         <v>65</v>
       </c>
       <c r="J49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K49" t="s">
         <v>3</v>
@@ -2012,13 +2011,13 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H50" t="s">
         <v>97</v>
       </c>
       <c r="J50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K50" t="s">
         <v>5</v>
@@ -2032,13 +2031,13 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H51" t="s">
         <v>97</v>
       </c>
       <c r="J51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K51" t="s">
         <v>3</v>
@@ -2052,13 +2051,13 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H52" t="s">
         <v>97</v>
       </c>
       <c r="J52" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K52" t="s">
         <v>5</v>
@@ -2072,13 +2071,13 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H53" t="s">
         <v>97</v>
       </c>
       <c r="J53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K53" t="s">
         <v>5</v>
@@ -2092,13 +2091,13 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H54" t="s">
         <v>97</v>
       </c>
       <c r="J54" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K54" t="s">
         <v>5</v>
@@ -2112,13 +2111,13 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H55" t="s">
         <v>97</v>
       </c>
       <c r="J55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K55" t="s">
         <v>5</v>
@@ -2129,13 +2128,13 @@
     </row>
     <row r="56" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J56" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K56" t="s">
         <v>5</v>
@@ -2149,13 +2148,13 @@
         <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F57" t="s">
         <v>63</v>
       </c>
       <c r="J57" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K57" t="s">
         <v>5</v>
@@ -2169,13 +2168,13 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F58" t="s">
         <v>63</v>
       </c>
       <c r="J58" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K58" t="s">
         <v>5</v>
@@ -2189,13 +2188,13 @@
         <v>88</v>
       </c>
       <c r="B59" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C59" t="s">
         <v>89</v>
       </c>
       <c r="J59" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K59" t="s">
         <v>3</v>
@@ -2209,19 +2208,19 @@
         <v>31</v>
       </c>
       <c r="B60" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C60" t="s">
         <v>141</v>
       </c>
       <c r="J60" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K60" t="s">
         <v>3</v>
       </c>
       <c r="L60" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -2229,19 +2228,19 @@
         <v>140</v>
       </c>
       <c r="B61" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
         <v>141</v>
       </c>
       <c r="J61" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K61" t="s">
         <v>3</v>
       </c>
       <c r="L61" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -2249,13 +2248,13 @@
         <v>90</v>
       </c>
       <c r="B62" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C62" t="s">
         <v>91</v>
       </c>
       <c r="J62" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K62" t="s">
         <v>3</v>
@@ -2269,13 +2268,13 @@
         <v>93</v>
       </c>
       <c r="B63" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E63" t="s">
         <v>94</v>
       </c>
       <c r="J63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K63" t="s">
         <v>3</v>
@@ -2289,10 +2288,10 @@
         <v>104</v>
       </c>
       <c r="B64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J64" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K64" t="s">
         <v>3</v>
@@ -2306,13 +2305,13 @@
         <v>137</v>
       </c>
       <c r="B65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C65" t="s">
         <v>87</v>
       </c>
       <c r="J65" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K65" t="s">
         <v>3</v>
@@ -2326,13 +2325,13 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C66" t="s">
         <v>70</v>
       </c>
       <c r="J66" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K66" t="s">
         <v>3</v>
@@ -2346,13 +2345,13 @@
         <v>128</v>
       </c>
       <c r="B67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C67" t="s">
         <v>70</v>
       </c>
       <c r="J67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K67" t="s">
         <v>3</v>
@@ -2366,10 +2365,10 @@
         <v>132</v>
       </c>
       <c r="B68" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J68" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K68" t="s">
         <v>5</v>
@@ -2383,10 +2382,10 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J69" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K69" t="s">
         <v>3</v>
@@ -2400,10 +2399,10 @@
         <v>134</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J70" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K70" t="s">
         <v>3</v>
@@ -2417,10 +2416,10 @@
         <v>136</v>
       </c>
       <c r="B71" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J71" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K71" t="s">
         <v>3</v>
@@ -2434,10 +2433,10 @@
         <v>138</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J72" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K72" t="s">
         <v>3</v>
@@ -2451,13 +2450,13 @@
         <v>142</v>
       </c>
       <c r="B73" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E73" t="s">
         <v>94</v>
       </c>
       <c r="J73" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K73" t="s">
         <v>3</v>
@@ -2471,10 +2470,10 @@
         <v>143</v>
       </c>
       <c r="B74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J74" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K74" t="s">
         <v>5</v>
@@ -2488,13 +2487,13 @@
         <v>145</v>
       </c>
       <c r="B75" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F75" t="s">
         <v>40</v>
       </c>
       <c r="J75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K75" t="s">
         <v>5</v>
@@ -2505,16 +2504,16 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B76" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E76" t="s">
         <v>96</v>
       </c>
       <c r="J76" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K76" t="s">
         <v>5</v>
@@ -2525,16 +2524,16 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B77" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H77" t="s">
         <v>131</v>
       </c>
       <c r="J77" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K77" t="s">
         <v>5</v>
@@ -2545,16 +2544,16 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B78" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H78" t="s">
         <v>131</v>
       </c>
       <c r="J78" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K78" t="s">
         <v>5</v>
@@ -2565,13 +2564,13 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B79" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J79" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K79" t="s">
         <v>5</v>
@@ -2582,13 +2581,13 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B80" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J80" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K80" t="s">
         <v>3</v>
@@ -2599,16 +2598,16 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B81" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I81" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J81" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K81" t="s">
         <v>3</v>
@@ -2619,16 +2618,16 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>166</v>
+      </c>
+      <c r="B82" t="s">
+        <v>146</v>
+      </c>
+      <c r="F82" t="s">
         <v>167</v>
       </c>
-      <c r="B82" t="s">
-        <v>147</v>
-      </c>
-      <c r="F82" t="s">
-        <v>168</v>
-      </c>
       <c r="J82" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K82" t="s">
         <v>5</v>
@@ -2639,22 +2638,22 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
       <c r="J83" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K83" s="5" t="s">
         <v>5</v>
@@ -2665,10 +2664,10 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
@@ -2678,7 +2677,7 @@
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
       <c r="J84" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K84" s="5" t="s">
         <v>5</v>
@@ -2689,22 +2688,22 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
       <c r="J85" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K85" s="5" t="s">
         <v>5</v>
@@ -2715,10 +2714,10 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
@@ -2728,7 +2727,7 @@
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K86" s="5" t="s">
         <v>5</v>
@@ -2739,22 +2738,22 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K87" s="5" t="s">
         <v>3</v>
@@ -2765,22 +2764,22 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
       <c r="J88" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K88" s="5" t="s">
         <v>3</v>
@@ -2791,10 +2790,10 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
@@ -2804,7 +2803,7 @@
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K89" s="5" t="s">
         <v>3</v>
@@ -2815,10 +2814,10 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
@@ -2828,7 +2827,7 @@
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K90" s="5" t="s">
         <v>3</v>
@@ -2839,10 +2838,10 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
@@ -2852,24 +2851,24 @@
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
       <c r="J91" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K91" s="5" t="s">
         <v>5</v>
       </c>
       <c r="L91" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J92" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K92" s="5" t="s">
         <v>5</v>
@@ -2880,30 +2879,30 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B93" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J93" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K93" s="5" t="s">
         <v>3</v>
       </c>
       <c r="L93" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J94" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K94" s="5" t="s">
         <v>5</v>
@@ -2914,13 +2913,13 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K95" s="5" t="s">
         <v>3</v>
@@ -2931,30 +2930,30 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J96" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K96" s="5" t="s">
         <v>3</v>
       </c>
       <c r="L96" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J97" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K97" s="5" t="s">
         <v>3</v>
@@ -2965,13 +2964,13 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J98" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K98" s="5" t="s">
         <v>5</v>
@@ -2982,13 +2981,13 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K99" s="5" t="s">
         <v>5</v>
@@ -2999,13 +2998,13 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J100" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K100" s="5" t="s">
         <v>5</v>
@@ -3016,13 +3015,13 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K101" s="5" t="s">
         <v>5</v>
@@ -3033,13 +3032,13 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K102" s="5" t="s">
         <v>5</v>
@@ -3050,30 +3049,30 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K103" s="5" t="s">
         <v>3</v>
       </c>
       <c r="L103" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K104" s="5" t="s">
         <v>5</v>
@@ -3084,16 +3083,16 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F105" t="s">
         <v>63</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K105" s="5" t="s">
         <v>5</v>

--- a/EUt.xlsx
+++ b/EUt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Medina_Admin\Desktop\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A10FCC-7C47-4272-A9A1-39049E7E3BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23191DE5-73FF-4C75-B3B3-1B50AA797D33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25395" yWindow="2445" windowWidth="21855" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -632,7 +632,7 @@
     <t>Media</t>
   </si>
   <si>
-    <t>Accelerate Beteiligung</t>
+    <t>Accelerate  Beteiligung</t>
   </si>
 </sst>
 </file>
